--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8394C1FF-3323-4084-91F0-6BF9593CA56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D659D5-7F35-4733-A282-82789B9A2CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="630" windowWidth="20565" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arm 3.5" sheetId="26" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>ลำดับ</t>
   </si>
   <si>
-    <t>ใบตรวจสอบเครื่อง ARM 3.5</t>
-  </si>
-  <si>
     <t>ผู้รับผิดชอบ : ไพรัตน์ อยู่พุ่มพฤกษ์</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t xml:space="preserve"> QC-AC-004</t>
+  </si>
+  <si>
+    <t>ใบตรวจสอบเครื่อง CIMCORE ARM 3.5 ( QC-AC-004)</t>
   </si>
 </sst>
 </file>
@@ -385,12 +385,21 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -411,15 +420,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1476,80 +1476,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="23"/>
-      <c r="AA2" s="23"/>
-      <c r="AB2" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1587,49 +1587,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
     </row>
     <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="10">
         <v>1</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -1768,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -1807,7 +1807,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -1846,7 +1846,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -1922,139 +1922,139 @@
     <row r="11" spans="1:33" ht="22.5" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="21"/>
-      <c r="AG11" s="21"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
     </row>
     <row r="12" spans="1:33" ht="22.5" customHeight="1">
       <c r="B12" s="5"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="23"/>
+      <c r="AF12" s="23"/>
+      <c r="AG12" s="23"/>
     </row>
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="B13" s="5"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="5"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
     </row>
     <row r="15" spans="1:33" ht="19.5" customHeight="1">
       <c r="B15" s="19" t="s">
@@ -2068,20 +2068,20 @@
     <row r="18" spans="3:33" ht="21">
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="24"/>
+      <c r="AG18" s="24"/>
     </row>
     <row r="19" spans="3:33" ht="29.25" customHeight="1">
-      <c r="AC19" s="31" t="s">
+      <c r="AC19" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="AD19" s="31"/>
-      <c r="AE19" s="31"/>
-      <c r="AF19" s="31"/>
-      <c r="AG19" s="31"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
     </row>
     <row r="20" spans="3:33" ht="14.25" customHeight="1">
       <c r="C20" s="3"/>
@@ -2091,30 +2091,36 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="AC19:AG19"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AC18:AG18"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="AG11:AG12"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
@@ -2131,36 +2137,30 @@
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="AE11:AE12"/>
     <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="AC19:AG19"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="AC18:AG18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D659D5-7F35-4733-A282-82789B9A2CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB81D00-39D6-4BF0-953A-5765B5C00FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -382,44 +382,44 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1476,80 +1476,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="27" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
+      <c r="AF1" s="21"/>
+      <c r="AG1" s="21"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="27" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1587,49 +1587,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="26"/>
     </row>
     <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="29"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10">
         <v>1</v>
       </c>
@@ -1922,139 +1922,139 @@
     <row r="11" spans="1:33" ht="22.5" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="27"/>
+      <c r="AF11" s="27"/>
+      <c r="AG11" s="27"/>
     </row>
     <row r="12" spans="1:33" ht="22.5" customHeight="1">
       <c r="B12" s="5"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-      <c r="AC12" s="23"/>
-      <c r="AD12" s="23"/>
-      <c r="AE12" s="23"/>
-      <c r="AF12" s="23"/>
-      <c r="AG12" s="23"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="28"/>
     </row>
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="B13" s="5"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="5"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="28"/>
     </row>
     <row r="15" spans="1:33" ht="19.5" customHeight="1">
       <c r="B15" s="19" t="s">
@@ -2062,26 +2062,57 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="185.25" customHeight="1">
-      <c r="B16" s="20"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
     </row>
     <row r="17" spans="3:33" ht="23.25" customHeight="1"/>
     <row r="18" spans="3:33" ht="21">
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
     </row>
     <row r="19" spans="3:33" ht="29.25" customHeight="1">
-      <c r="AC19" s="21" t="s">
+      <c r="AC19" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
     </row>
     <row r="20" spans="3:33" ht="14.25" customHeight="1">
       <c r="C20" s="3"/>
@@ -2090,37 +2121,32 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
+  <mergeCells count="71">
+    <mergeCell ref="AC19:AG19"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="AC18:AG18"/>
+    <mergeCell ref="B16:AG16"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
     <mergeCell ref="AG11:AG12"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
@@ -2137,30 +2163,36 @@
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="AE11:AE12"/>
     <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="AC19:AG19"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AC18:AG18"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -331,7 +331,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -430,6 +430,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1770,8 +1776,16 @@
       <c r="AB6" s="22" t="n"/>
       <c r="AC6" s="22" t="n"/>
       <c r="AD6" s="22" t="n"/>
-      <c r="AE6" s="22" t="n"/>
-      <c r="AF6" s="22" t="n"/>
+      <c r="AE6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="22" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1811,8 +1825,16 @@
       <c r="AB7" s="22" t="n"/>
       <c r="AC7" s="22" t="n"/>
       <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
+      <c r="AE7" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="22" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1852,8 +1874,16 @@
       <c r="AB8" s="22" t="n"/>
       <c r="AC8" s="22" t="n"/>
       <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="22" t="n"/>
+      <c r="AE8" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF8" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AG8" s="22" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1893,8 +1923,16 @@
       <c r="AB9" s="22" t="n"/>
       <c r="AC9" s="22" t="n"/>
       <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="22" t="n"/>
-      <c r="AF9" s="22" t="n"/>
+      <c r="AE9" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="22" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1934,8 +1972,16 @@
       <c r="AB10" s="22" t="n"/>
       <c r="AC10" s="22" t="n"/>
       <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="22" t="n"/>
-      <c r="AF10" s="22" t="n"/>
+      <c r="AE10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="22" t="n"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -1969,8 +2015,16 @@
       <c r="AB11" s="38" t="n"/>
       <c r="AC11" s="38" t="n"/>
       <c r="AD11" s="38" t="n"/>
-      <c r="AE11" s="38" t="n"/>
-      <c r="AF11" s="38" t="n"/>
+      <c r="AE11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไพรัตน์ </t>
+        </is>
+      </c>
+      <c r="AF11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไพรัตน์ </t>
+        </is>
+      </c>
       <c r="AG11" s="38" t="n"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -2083,7 +2137,11 @@
       </c>
     </row>
     <row r="16" ht="185.25" customHeight="1">
-      <c r="B16" s="32" t="n"/>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก,  [วันที่ 30]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.25" customHeight="1"/>
     <row r="18" ht="21" customHeight="1">

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -1786,7 +1786,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG6" s="22" t="n"/>
+      <c r="AG6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A7" s="8" t="n">
@@ -1835,7 +1839,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG7" s="22" t="n"/>
+      <c r="AG7" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A8" s="8" t="n">
@@ -1884,7 +1892,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG8" s="22" t="n"/>
+      <c r="AG8" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A9" s="8" t="n">
@@ -1933,7 +1945,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG9" s="22" t="n"/>
+      <c r="AG9" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A10" s="8" t="n">
@@ -1982,7 +1998,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG10" s="22" t="n"/>
+      <c r="AG10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="7" t="n"/>
@@ -2025,7 +2045,11 @@
           <t xml:space="preserve">ไพรัตน์ </t>
         </is>
       </c>
-      <c r="AG11" s="38" t="n"/>
+      <c r="AG11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไพรัตน์ </t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="B12" s="5" t="n"/>
@@ -2139,7 +2163,7 @@
     <row r="16" ht="185.25" customHeight="1">
       <c r="B16" s="41" t="inlineStr">
         <is>
-          <t>[วันที่ 29]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก,  [วันที่ 30]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก</t>
+          <t>[วันที่ 29]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก,  [วันที่ 30]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก,  [วันที่ 31]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -1748,49 +1748,37 @@
           <t>ตรวจดูสภาพของสายไฟ</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="22" t="n"/>
-      <c r="I6" s="22" t="n"/>
-      <c r="J6" s="22" t="n"/>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="22" t="n"/>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n"/>
-      <c r="P6" s="22" t="n"/>
-      <c r="Q6" s="22" t="n"/>
-      <c r="R6" s="22" t="n"/>
-      <c r="S6" s="22" t="n"/>
-      <c r="T6" s="22" t="n"/>
-      <c r="U6" s="22" t="n"/>
-      <c r="V6" s="22" t="n"/>
-      <c r="W6" s="22" t="n"/>
-      <c r="X6" s="22" t="n"/>
-      <c r="Y6" s="22" t="n"/>
-      <c r="Z6" s="22" t="n"/>
-      <c r="AA6" s="22" t="n"/>
-      <c r="AB6" s="22" t="n"/>
-      <c r="AC6" s="22" t="n"/>
-      <c r="AD6" s="22" t="n"/>
-      <c r="AE6" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr"/>
+      <c r="J6" s="22" t="inlineStr"/>
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="22" t="inlineStr"/>
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="22" t="inlineStr"/>
+      <c r="P6" s="22" t="inlineStr"/>
+      <c r="Q6" s="22" t="inlineStr"/>
+      <c r="R6" s="22" t="inlineStr"/>
+      <c r="S6" s="22" t="inlineStr"/>
+      <c r="T6" s="22" t="inlineStr"/>
+      <c r="U6" s="22" t="inlineStr"/>
+      <c r="V6" s="22" t="inlineStr"/>
+      <c r="W6" s="22" t="inlineStr"/>
+      <c r="X6" s="22" t="inlineStr"/>
+      <c r="Y6" s="22" t="inlineStr"/>
+      <c r="Z6" s="22" t="inlineStr"/>
+      <c r="AA6" s="22" t="inlineStr"/>
+      <c r="AB6" s="22" t="inlineStr"/>
+      <c r="AC6" s="22" t="inlineStr"/>
+      <c r="AD6" s="22" t="inlineStr"/>
+      <c r="AE6" s="22" t="inlineStr"/>
+      <c r="AF6" s="22" t="inlineStr"/>
+      <c r="AG6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A7" s="8" t="n">
@@ -1801,49 +1789,37 @@
           <t>ตรวจดูสภาพ ARM ของเครื่อง</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C7" s="22" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr"/>
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
+      <c r="J7" s="22" t="inlineStr"/>
+      <c r="K7" s="22" t="inlineStr"/>
+      <c r="L7" s="22" t="inlineStr"/>
+      <c r="M7" s="22" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="22" t="inlineStr"/>
+      <c r="P7" s="22" t="inlineStr"/>
+      <c r="Q7" s="22" t="inlineStr"/>
+      <c r="R7" s="22" t="inlineStr"/>
+      <c r="S7" s="22" t="inlineStr"/>
+      <c r="T7" s="22" t="inlineStr"/>
+      <c r="U7" s="22" t="inlineStr"/>
+      <c r="V7" s="22" t="inlineStr"/>
+      <c r="W7" s="22" t="inlineStr"/>
+      <c r="X7" s="22" t="inlineStr"/>
+      <c r="Y7" s="22" t="inlineStr"/>
+      <c r="Z7" s="22" t="inlineStr"/>
+      <c r="AA7" s="22" t="inlineStr"/>
+      <c r="AB7" s="22" t="inlineStr"/>
+      <c r="AC7" s="22" t="inlineStr"/>
+      <c r="AD7" s="22" t="inlineStr"/>
+      <c r="AE7" s="22" t="inlineStr"/>
+      <c r="AF7" s="22" t="inlineStr"/>
+      <c r="AG7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A8" s="8" t="n">
@@ -1854,49 +1830,37 @@
           <t>ตรวจดูสภาพของหัว PROBE คตงอหรือไม่</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n"/>
-      <c r="T8" s="22" t="n"/>
-      <c r="U8" s="22" t="n"/>
-      <c r="V8" s="22" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="22" t="n"/>
-      <c r="Y8" s="22" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="22" t="n"/>
-      <c r="AB8" s="22" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF8" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG8" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C8" s="22" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr"/>
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr"/>
+      <c r="J8" s="22" t="inlineStr"/>
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="22" t="inlineStr"/>
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="22" t="inlineStr"/>
+      <c r="P8" s="22" t="inlineStr"/>
+      <c r="Q8" s="22" t="inlineStr"/>
+      <c r="R8" s="22" t="inlineStr"/>
+      <c r="S8" s="22" t="inlineStr"/>
+      <c r="T8" s="22" t="inlineStr"/>
+      <c r="U8" s="22" t="inlineStr"/>
+      <c r="V8" s="22" t="inlineStr"/>
+      <c r="W8" s="22" t="inlineStr"/>
+      <c r="X8" s="22" t="inlineStr"/>
+      <c r="Y8" s="22" t="inlineStr"/>
+      <c r="Z8" s="22" t="inlineStr"/>
+      <c r="AA8" s="22" t="inlineStr"/>
+      <c r="AB8" s="22" t="inlineStr"/>
+      <c r="AC8" s="22" t="inlineStr"/>
+      <c r="AD8" s="22" t="inlineStr"/>
+      <c r="AE8" s="22" t="inlineStr"/>
+      <c r="AF8" s="22" t="inlineStr"/>
+      <c r="AG8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A9" s="8" t="n">
@@ -1907,49 +1871,37 @@
           <t>ตรวจสอบ STICKER</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="22" t="n"/>
-      <c r="R9" s="22" t="n"/>
-      <c r="S9" s="22" t="n"/>
-      <c r="T9" s="22" t="n"/>
-      <c r="U9" s="22" t="n"/>
-      <c r="V9" s="22" t="n"/>
-      <c r="W9" s="22" t="n"/>
-      <c r="X9" s="22" t="n"/>
-      <c r="Y9" s="22" t="n"/>
-      <c r="Z9" s="22" t="n"/>
-      <c r="AA9" s="22" t="n"/>
-      <c r="AB9" s="22" t="n"/>
-      <c r="AC9" s="22" t="n"/>
-      <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C9" s="22" t="inlineStr"/>
+      <c r="D9" s="22" t="inlineStr"/>
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr"/>
+      <c r="J9" s="22" t="inlineStr"/>
+      <c r="K9" s="22" t="inlineStr"/>
+      <c r="L9" s="22" t="inlineStr"/>
+      <c r="M9" s="22" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr"/>
+      <c r="O9" s="22" t="inlineStr"/>
+      <c r="P9" s="22" t="inlineStr"/>
+      <c r="Q9" s="22" t="inlineStr"/>
+      <c r="R9" s="22" t="inlineStr"/>
+      <c r="S9" s="22" t="inlineStr"/>
+      <c r="T9" s="22" t="inlineStr"/>
+      <c r="U9" s="22" t="inlineStr"/>
+      <c r="V9" s="22" t="inlineStr"/>
+      <c r="W9" s="22" t="inlineStr"/>
+      <c r="X9" s="22" t="inlineStr"/>
+      <c r="Y9" s="22" t="inlineStr"/>
+      <c r="Z9" s="22" t="inlineStr"/>
+      <c r="AA9" s="22" t="inlineStr"/>
+      <c r="AB9" s="22" t="inlineStr"/>
+      <c r="AC9" s="22" t="inlineStr"/>
+      <c r="AD9" s="22" t="inlineStr"/>
+      <c r="AE9" s="22" t="inlineStr"/>
+      <c r="AF9" s="22" t="inlineStr"/>
+      <c r="AG9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A10" s="8" t="n">
@@ -1960,96 +1912,72 @@
           <t>ตรวจสอบNOTEBOOK COMPUTER</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="22" t="n"/>
-      <c r="R10" s="22" t="n"/>
-      <c r="S10" s="22" t="n"/>
-      <c r="T10" s="22" t="n"/>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="22" t="n"/>
-      <c r="W10" s="22" t="n"/>
-      <c r="X10" s="22" t="n"/>
-      <c r="Y10" s="22" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="22" t="n"/>
-      <c r="AB10" s="22" t="n"/>
-      <c r="AC10" s="22" t="n"/>
-      <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C10" s="22" t="inlineStr"/>
+      <c r="D10" s="22" t="inlineStr"/>
+      <c r="E10" s="22" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr"/>
+      <c r="J10" s="22" t="inlineStr"/>
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="22" t="inlineStr"/>
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="22" t="inlineStr"/>
+      <c r="P10" s="22" t="inlineStr"/>
+      <c r="Q10" s="22" t="inlineStr"/>
+      <c r="R10" s="22" t="inlineStr"/>
+      <c r="S10" s="22" t="inlineStr"/>
+      <c r="T10" s="22" t="inlineStr"/>
+      <c r="U10" s="22" t="inlineStr"/>
+      <c r="V10" s="22" t="inlineStr"/>
+      <c r="W10" s="22" t="inlineStr"/>
+      <c r="X10" s="22" t="inlineStr"/>
+      <c r="Y10" s="22" t="inlineStr"/>
+      <c r="Z10" s="22" t="inlineStr"/>
+      <c r="AA10" s="22" t="inlineStr"/>
+      <c r="AB10" s="22" t="inlineStr"/>
+      <c r="AC10" s="22" t="inlineStr"/>
+      <c r="AD10" s="22" t="inlineStr"/>
+      <c r="AE10" s="22" t="inlineStr"/>
+      <c r="AF10" s="22" t="inlineStr"/>
+      <c r="AG10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="38" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="38" t="n"/>
-      <c r="H11" s="38" t="n"/>
-      <c r="I11" s="38" t="n"/>
-      <c r="J11" s="38" t="n"/>
-      <c r="K11" s="38" t="n"/>
-      <c r="L11" s="38" t="n"/>
-      <c r="M11" s="38" t="n"/>
-      <c r="N11" s="38" t="n"/>
-      <c r="O11" s="38" t="n"/>
-      <c r="P11" s="38" t="n"/>
-      <c r="Q11" s="38" t="n"/>
-      <c r="R11" s="38" t="n"/>
-      <c r="S11" s="38" t="n"/>
-      <c r="T11" s="38" t="n"/>
-      <c r="U11" s="38" t="n"/>
-      <c r="V11" s="38" t="n"/>
-      <c r="W11" s="38" t="n"/>
-      <c r="X11" s="38" t="n"/>
-      <c r="Y11" s="38" t="n"/>
-      <c r="Z11" s="38" t="n"/>
-      <c r="AA11" s="38" t="n"/>
-      <c r="AB11" s="38" t="n"/>
-      <c r="AC11" s="38" t="n"/>
-      <c r="AD11" s="38" t="n"/>
-      <c r="AE11" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไพรัตน์ </t>
-        </is>
-      </c>
-      <c r="AF11" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไพรัตน์ </t>
-        </is>
-      </c>
-      <c r="AG11" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไพรัตน์ </t>
-        </is>
-      </c>
+      <c r="C11" s="38" t="inlineStr"/>
+      <c r="D11" s="38" t="inlineStr"/>
+      <c r="E11" s="38" t="inlineStr"/>
+      <c r="F11" s="38" t="inlineStr"/>
+      <c r="G11" s="38" t="inlineStr"/>
+      <c r="H11" s="38" t="inlineStr"/>
+      <c r="I11" s="38" t="inlineStr"/>
+      <c r="J11" s="38" t="inlineStr"/>
+      <c r="K11" s="38" t="inlineStr"/>
+      <c r="L11" s="38" t="inlineStr"/>
+      <c r="M11" s="38" t="inlineStr"/>
+      <c r="N11" s="38" t="inlineStr"/>
+      <c r="O11" s="38" t="inlineStr"/>
+      <c r="P11" s="38" t="inlineStr"/>
+      <c r="Q11" s="38" t="inlineStr"/>
+      <c r="R11" s="38" t="inlineStr"/>
+      <c r="S11" s="38" t="inlineStr"/>
+      <c r="T11" s="38" t="inlineStr"/>
+      <c r="U11" s="38" t="inlineStr"/>
+      <c r="V11" s="38" t="inlineStr"/>
+      <c r="W11" s="38" t="inlineStr"/>
+      <c r="X11" s="38" t="inlineStr"/>
+      <c r="Y11" s="38" t="inlineStr"/>
+      <c r="Z11" s="38" t="inlineStr"/>
+      <c r="AA11" s="38" t="inlineStr"/>
+      <c r="AB11" s="38" t="inlineStr"/>
+      <c r="AC11" s="38" t="inlineStr"/>
+      <c r="AD11" s="38" t="inlineStr"/>
+      <c r="AE11" s="40" t="inlineStr"/>
+      <c r="AF11" s="40" t="inlineStr"/>
+      <c r="AG11" s="40" t="inlineStr"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="B12" s="5" t="n"/>
@@ -2087,37 +2015,37 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="28" t="n"/>
-      <c r="J13" s="28" t="n"/>
-      <c r="K13" s="28" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="28" t="n"/>
-      <c r="N13" s="28" t="n"/>
-      <c r="O13" s="28" t="n"/>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="28" t="n"/>
-      <c r="S13" s="28" t="n"/>
-      <c r="T13" s="28" t="n"/>
-      <c r="U13" s="28" t="n"/>
-      <c r="V13" s="28" t="n"/>
-      <c r="W13" s="28" t="n"/>
-      <c r="X13" s="28" t="n"/>
-      <c r="Y13" s="28" t="n"/>
-      <c r="Z13" s="28" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="28" t="n"/>
-      <c r="AD13" s="28" t="n"/>
-      <c r="AE13" s="28" t="n"/>
-      <c r="AF13" s="28" t="n"/>
-      <c r="AG13" s="28" t="n"/>
+      <c r="C13" s="28" t="inlineStr"/>
+      <c r="D13" s="28" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr"/>
+      <c r="F13" s="28" t="inlineStr"/>
+      <c r="G13" s="28" t="inlineStr"/>
+      <c r="H13" s="28" t="inlineStr"/>
+      <c r="I13" s="28" t="inlineStr"/>
+      <c r="J13" s="28" t="inlineStr"/>
+      <c r="K13" s="28" t="inlineStr"/>
+      <c r="L13" s="28" t="inlineStr"/>
+      <c r="M13" s="28" t="inlineStr"/>
+      <c r="N13" s="28" t="inlineStr"/>
+      <c r="O13" s="28" t="inlineStr"/>
+      <c r="P13" s="28" t="inlineStr"/>
+      <c r="Q13" s="28" t="inlineStr"/>
+      <c r="R13" s="28" t="inlineStr"/>
+      <c r="S13" s="28" t="inlineStr"/>
+      <c r="T13" s="28" t="inlineStr"/>
+      <c r="U13" s="28" t="inlineStr"/>
+      <c r="V13" s="28" t="inlineStr"/>
+      <c r="W13" s="28" t="inlineStr"/>
+      <c r="X13" s="28" t="inlineStr"/>
+      <c r="Y13" s="28" t="inlineStr"/>
+      <c r="Z13" s="28" t="inlineStr"/>
+      <c r="AA13" s="28" t="inlineStr"/>
+      <c r="AB13" s="28" t="inlineStr"/>
+      <c r="AC13" s="28" t="inlineStr"/>
+      <c r="AD13" s="28" t="inlineStr"/>
+      <c r="AE13" s="28" t="inlineStr"/>
+      <c r="AF13" s="28" t="inlineStr"/>
+      <c r="AG13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="5" t="n"/>
@@ -2161,11 +2089,7 @@
       </c>
     </row>
     <row r="16" ht="185.25" customHeight="1">
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t>[วันที่ 29]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก,  [วันที่ 30]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก,  [วันที่ 31]: ขา arm ชำรุด, 1 PROBE 3 สึก 2 หัวเข็มปลายแตก</t>
-        </is>
-      </c>
+      <c r="B16" s="41" t="inlineStr"/>
     </row>
     <row r="17" ht="23.25" customHeight="1"/>
     <row r="18" ht="21" customHeight="1">
@@ -2211,8 +2135,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -2135,8 +2135,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="P11:P12"/>
     <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="P11:P12"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -2135,8 +2135,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -1752,7 +1752,11 @@
       <c r="D6" s="22" t="inlineStr"/>
       <c r="E6" s="22" t="inlineStr"/>
       <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="H6" s="22" t="inlineStr"/>
       <c r="I6" s="22" t="inlineStr"/>
       <c r="J6" s="22" t="inlineStr"/>
@@ -1793,7 +1797,11 @@
       <c r="D7" s="22" t="inlineStr"/>
       <c r="E7" s="22" t="inlineStr"/>
       <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="22" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="H7" s="22" t="inlineStr"/>
       <c r="I7" s="22" t="inlineStr"/>
       <c r="J7" s="22" t="inlineStr"/>
@@ -1834,7 +1842,11 @@
       <c r="D8" s="22" t="inlineStr"/>
       <c r="E8" s="22" t="inlineStr"/>
       <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="22" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="H8" s="22" t="inlineStr"/>
       <c r="I8" s="22" t="inlineStr"/>
       <c r="J8" s="22" t="inlineStr"/>
@@ -1875,7 +1887,11 @@
       <c r="D9" s="22" t="inlineStr"/>
       <c r="E9" s="22" t="inlineStr"/>
       <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="22" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="H9" s="22" t="inlineStr"/>
       <c r="I9" s="22" t="inlineStr"/>
       <c r="J9" s="22" t="inlineStr"/>
@@ -1916,7 +1932,11 @@
       <c r="D10" s="22" t="inlineStr"/>
       <c r="E10" s="22" t="inlineStr"/>
       <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="H10" s="22" t="inlineStr"/>
       <c r="I10" s="22" t="inlineStr"/>
       <c r="J10" s="22" t="inlineStr"/>
@@ -1951,7 +1971,11 @@
       <c r="D11" s="38" t="inlineStr"/>
       <c r="E11" s="38" t="inlineStr"/>
       <c r="F11" s="38" t="inlineStr"/>
-      <c r="G11" s="38" t="inlineStr"/>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไพรัตน์ </t>
+        </is>
+      </c>
       <c r="H11" s="38" t="inlineStr"/>
       <c r="I11" s="38" t="inlineStr"/>
       <c r="J11" s="38" t="inlineStr"/>
@@ -2089,7 +2113,11 @@
       </c>
     </row>
     <row r="16" ht="185.25" customHeight="1">
-      <c r="B16" s="41" t="inlineStr"/>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>[วันที่ 5]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.25" customHeight="1"/>
     <row r="18" ht="21" customHeight="1">
@@ -2135,8 +2163,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -1757,7 +1757,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="22" t="inlineStr"/>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr"/>
@@ -1802,7 +1806,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I7" s="22" t="inlineStr"/>
       <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
@@ -1847,7 +1855,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I8" s="22" t="inlineStr"/>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr"/>
@@ -1892,7 +1904,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I9" s="22" t="inlineStr"/>
       <c r="J9" s="22" t="inlineStr"/>
       <c r="K9" s="22" t="inlineStr"/>
@@ -1937,7 +1953,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="22" t="inlineStr"/>
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr"/>
@@ -1976,7 +1996,11 @@
           <t xml:space="preserve">ไพรัตน์ </t>
         </is>
       </c>
-      <c r="H11" s="38" t="inlineStr"/>
+      <c r="H11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไพรัตน์ </t>
+        </is>
+      </c>
       <c r="I11" s="38" t="inlineStr"/>
       <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
@@ -2115,7 +2139,7 @@
     <row r="16" ht="185.25" customHeight="1">
       <c r="B16" s="41" t="inlineStr">
         <is>
-          <t>[วันที่ 5]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ</t>
+          <t>[วันที่ 5]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ,  [วันที่ 6]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ, ข้อ 4: ส่งสอบเทียบ</t>
         </is>
       </c>
     </row>
@@ -2163,8 +2187,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="P11:P12"/>
     <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="P11:P12"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -331,7 +331,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -435,6 +435,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2068,7 +2071,11 @@
       <c r="E13" s="28" t="inlineStr"/>
       <c r="F13" s="28" t="inlineStr"/>
       <c r="G13" s="28" t="inlineStr"/>
-      <c r="H13" s="28" t="inlineStr"/>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>ณรงค์ชัย</t>
+        </is>
+      </c>
       <c r="I13" s="28" t="inlineStr"/>
       <c r="J13" s="28" t="inlineStr"/>
       <c r="K13" s="28" t="inlineStr"/>
@@ -2187,8 +2194,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -1765,7 +1765,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr"/>
       <c r="L6" s="22" t="inlineStr"/>
@@ -1814,7 +1818,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
       <c r="L7" s="22" t="inlineStr"/>
@@ -1863,7 +1871,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr"/>
       <c r="L8" s="22" t="inlineStr"/>
@@ -1912,7 +1924,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="22" t="inlineStr"/>
       <c r="K9" s="22" t="inlineStr"/>
       <c r="L9" s="22" t="inlineStr"/>
@@ -1961,7 +1977,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr"/>
       <c r="L10" s="22" t="inlineStr"/>
@@ -2004,7 +2024,11 @@
           <t xml:space="preserve">ไพรัตน์ </t>
         </is>
       </c>
-      <c r="I11" s="38" t="inlineStr"/>
+      <c r="I11" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไพรัตน์ </t>
+        </is>
+      </c>
       <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
       <c r="L11" s="38" t="inlineStr"/>
@@ -2146,7 +2170,7 @@
     <row r="16" ht="185.25" customHeight="1">
       <c r="B16" s="41" t="inlineStr">
         <is>
-          <t>[วันที่ 5]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ,  [วันที่ 6]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ, ข้อ 4: ส่งสอบเทียบ</t>
+          <t>[วันที่ 5]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ,  [วันที่ 6]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบ, ข้อ 4: ส่งสอบเทียบ,  [วันที่ 7]: ข้อ 2: ส่งสอบเทียบ, ข้อ 3: ส่งสอบเทียบส่งสอบเทียบ</t>
         </is>
       </c>
     </row>
@@ -2194,8 +2218,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="P11:P12"/>
     <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="P11:P12"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-21.xlsx
+++ b/FM-MN-07_QC-21.xlsx
@@ -1772,7 +1772,11 @@
       </c>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="22" t="inlineStr"/>
       <c r="N6" s="22" t="inlineStr"/>
       <c r="O6" s="22" t="inlineStr"/>
@@ -1825,7 +1829,11 @@
       </c>
       <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
-      <c r="L7" s="22" t="inlineStr"/>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="22" t="inlineStr"/>
       <c r="N7" s="22" t="inlineStr"/>
       <c r="O7" s="22" t="inlineStr"/>
@@ -1878,7 +1886,11 @@
       </c>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="22" t="inlineStr"/>
       <c r="N8" s="22" t="inlineStr"/>
       <c r="O8" s="22" t="inlineStr"/>
@@ -1931,7 +1943,11 @@
       </c>
       <c r="J9" s="22" t="inlineStr"/>
       <c r="K9" s="22" t="inlineStr"/>
-      <c r="L9" s="22" t="inlineStr"/>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="22" t="inlineStr"/>
       <c r="N9" s="22" t="inlineStr"/>
       <c r="O9" s="22" t="inlineStr"/>
@@ -1984,7 +2000,11 @@
       </c>
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="22" t="inlineStr"/>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="22" t="inlineStr"/>
       <c r="N10" s="22" t="inlineStr"/>
       <c r="O10" s="22" t="inlineStr"/>
@@ -2031,7 +2051,11 @@
       </c>
       <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
-      <c r="L11" s="38" t="inlineStr"/>
+      <c r="L11" s="40" t="inlineStr">
+        <is>
+          <t>ปวีณ์กร</t>
+        </is>
+      </c>
       <c r="M11" s="38" t="inlineStr"/>
       <c r="N11" s="38" t="inlineStr"/>
       <c r="O11" s="38" t="inlineStr"/>
@@ -2218,8 +2242,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>
